--- a/Visualization/generation_validation/generation_data_0.5.xlsx
+++ b/Visualization/generation_validation/generation_data_0.5.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\博士论文\heatwave load forecasting\generation_data_proportion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="欧洲" sheetId="1" r:id="rId1"/>
@@ -32,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
   <si>
     <t>Counrty</t>
   </si>
   <si>
-    <t>MLP</t>
-  </si>
-  <si>
     <t>LSTM</t>
-  </si>
-  <si>
-    <t>CNN</t>
   </si>
   <si>
     <t>MAE</t>
@@ -1265,477 +1264,233 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>0.046127</v>
+        <v>0.039004</v>
       </c>
       <c r="C3">
-        <v>0.054614</v>
-      </c>
-      <c r="D3">
-        <v>0.039004</v>
-      </c>
-      <c r="E3">
         <v>0.050645</v>
-      </c>
-      <c r="F3">
-        <v>0.05629</v>
-      </c>
-      <c r="G3">
-        <v>0.080051</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>0.041437</v>
+        <v>0.041254</v>
       </c>
       <c r="C4">
-        <v>0.053078</v>
-      </c>
-      <c r="D4">
-        <v>0.041254</v>
-      </c>
-      <c r="E4">
         <v>0.048733</v>
-      </c>
-      <c r="F4">
-        <v>0.067357</v>
-      </c>
-      <c r="G4">
-        <v>0.07926</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>0.039241</v>
+        <v>0.035283</v>
       </c>
       <c r="C5">
-        <v>0.050407</v>
-      </c>
-      <c r="D5">
-        <v>0.035283</v>
-      </c>
-      <c r="E5">
         <v>0.043946</v>
-      </c>
-      <c r="F5">
-        <v>0.037155</v>
-      </c>
-      <c r="G5">
-        <v>0.046223</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0.019765</v>
+        <v>0.038027</v>
       </c>
       <c r="C6">
-        <v>0.024476</v>
-      </c>
-      <c r="D6">
-        <v>0.038027</v>
-      </c>
-      <c r="E6">
         <v>0.047579</v>
-      </c>
-      <c r="F6">
-        <v>0.025485</v>
-      </c>
-      <c r="G6">
-        <v>0.032743</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>0.029309</v>
+        <v>0.018154</v>
       </c>
       <c r="C7">
-        <v>0.037138</v>
-      </c>
-      <c r="D7">
-        <v>0.018154</v>
-      </c>
-      <c r="E7">
         <v>0.023401</v>
-      </c>
-      <c r="F7">
-        <v>0.021363</v>
-      </c>
-      <c r="G7">
-        <v>0.02626</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0.026148</v>
+        <v>0.028337</v>
       </c>
       <c r="C8">
-        <v>0.032552</v>
-      </c>
-      <c r="D8">
-        <v>0.028337</v>
-      </c>
-      <c r="E8">
         <v>0.035772</v>
-      </c>
-      <c r="F8">
-        <v>0.026614</v>
-      </c>
-      <c r="G8">
-        <v>0.035121</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>0.020575</v>
+        <v>0.025965</v>
       </c>
       <c r="C9">
-        <v>0.026678</v>
-      </c>
-      <c r="D9">
-        <v>0.025965</v>
-      </c>
-      <c r="E9">
         <v>0.032653</v>
-      </c>
-      <c r="F9">
-        <v>0.051981</v>
-      </c>
-      <c r="G9">
-        <v>0.057887</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>0.069062</v>
+        <v>0.062124</v>
       </c>
       <c r="C10">
-        <v>0.096738</v>
-      </c>
-      <c r="D10">
-        <v>0.062124</v>
-      </c>
-      <c r="E10">
         <v>0.078363</v>
-      </c>
-      <c r="F10">
-        <v>0.058074</v>
-      </c>
-      <c r="G10">
-        <v>0.073395</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>0.023471</v>
+        <v>0.022439</v>
       </c>
       <c r="C11">
-        <v>0.031666</v>
-      </c>
-      <c r="D11">
-        <v>0.022439</v>
-      </c>
-      <c r="E11">
         <v>0.029264</v>
-      </c>
-      <c r="F11">
-        <v>0.023427</v>
-      </c>
-      <c r="G11">
-        <v>0.030663</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>0.052923</v>
+        <v>0.035555</v>
       </c>
       <c r="C12">
-        <v>0.071702</v>
-      </c>
-      <c r="D12">
-        <v>0.035555</v>
-      </c>
-      <c r="E12">
         <v>0.044706</v>
-      </c>
-      <c r="F12">
-        <v>0.072394</v>
-      </c>
-      <c r="G12">
-        <v>0.078226</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>0.044135</v>
+        <v>0.032473</v>
       </c>
       <c r="C13">
-        <v>0.065904</v>
-      </c>
-      <c r="D13">
-        <v>0.032473</v>
-      </c>
-      <c r="E13">
         <v>0.044307</v>
-      </c>
-      <c r="F13">
-        <v>0.03486</v>
-      </c>
-      <c r="G13">
-        <v>0.04598</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.024736</v>
+        <v>0.031997</v>
       </c>
       <c r="C14">
-        <v>0.034148</v>
-      </c>
-      <c r="D14">
-        <v>0.031997</v>
-      </c>
-      <c r="E14">
         <v>0.043592</v>
-      </c>
-      <c r="F14">
-        <v>0.019306</v>
-      </c>
-      <c r="G14">
-        <v>0.027913</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>0.025997</v>
+        <v>0.022148</v>
       </c>
       <c r="C15">
-        <v>0.031266</v>
-      </c>
-      <c r="D15">
-        <v>0.022148</v>
-      </c>
-      <c r="E15">
         <v>0.02722</v>
-      </c>
-      <c r="F15">
-        <v>0.023199</v>
-      </c>
-      <c r="G15">
-        <v>0.028631</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>0.018535</v>
+      </c>
+      <c r="C16">
+        <v>0.026531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>0.028861</v>
+      </c>
+      <c r="C17">
+        <v>0.034943</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.022913</v>
-      </c>
-      <c r="C16">
-        <v>0.035314</v>
-      </c>
-      <c r="D16">
-        <v>0.018535</v>
-      </c>
-      <c r="E16">
-        <v>0.026531</v>
-      </c>
-      <c r="F16">
-        <v>0.023037</v>
-      </c>
-      <c r="G16">
-        <v>0.029814</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.038515</v>
+      </c>
+      <c r="C18">
+        <v>0.049065</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>0.032836</v>
-      </c>
-      <c r="C17">
-        <v>0.039562</v>
-      </c>
-      <c r="D17">
-        <v>0.028861</v>
-      </c>
-      <c r="E17">
-        <v>0.034943</v>
-      </c>
-      <c r="F17">
-        <v>0.036077</v>
-      </c>
-      <c r="G17">
-        <v>0.041546</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.034266</v>
+      </c>
+      <c r="C19">
+        <v>0.048791</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.04471</v>
-      </c>
-      <c r="C18">
-        <v>0.058111</v>
-      </c>
-      <c r="D18">
-        <v>0.038515</v>
-      </c>
-      <c r="E18">
-        <v>0.049065</v>
-      </c>
-      <c r="F18">
-        <v>0.039724</v>
-      </c>
-      <c r="G18">
-        <v>0.0485</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.042232</v>
+      </c>
+      <c r="C20">
+        <v>0.055519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.025552</v>
-      </c>
-      <c r="C19">
-        <v>0.033555</v>
-      </c>
-      <c r="D19">
-        <v>0.034266</v>
-      </c>
-      <c r="E19">
-        <v>0.048791</v>
-      </c>
-      <c r="F19">
-        <v>0.046207</v>
-      </c>
-      <c r="G19">
-        <v>0.05757</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
-        <v>0.041477</v>
-      </c>
-      <c r="C20">
-        <v>0.050785</v>
-      </c>
-      <c r="D20">
-        <v>0.042232</v>
-      </c>
-      <c r="E20">
-        <v>0.055519</v>
-      </c>
-      <c r="F20">
-        <v>0.039429</v>
-      </c>
-      <c r="G20">
-        <v>0.04852</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="B21">
-        <f>AVERAGE(B3:B20)</f>
-        <v>0.035023</v>
+        <f xml:space="preserve">AVERAGE(B3:B20)</f>
+        <v>0.0330649444444445</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="B21:G21" si="0">AVERAGE(C3:C20)</f>
-        <v>0.045983</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>0.0330649444444445</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C20)</f>
         <v>0.0425016666666667</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>0.0389988333333333</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
-        <v>0.0482390555555555</v>
       </c>
     </row>
   </sheetData>
@@ -1762,552 +1517,272 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>0.025614</v>
+        <v>0.022028</v>
       </c>
       <c r="C3">
-        <v>0.034995</v>
-      </c>
-      <c r="D3">
-        <v>0.022028</v>
-      </c>
-      <c r="E3">
         <v>0.030912</v>
-      </c>
-      <c r="F3">
-        <v>0.03066</v>
-      </c>
-      <c r="G3">
-        <v>0.03606</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>0.018772</v>
+        <v>0.018709</v>
       </c>
       <c r="C4">
-        <v>0.025835</v>
-      </c>
-      <c r="D4">
-        <v>0.018709</v>
-      </c>
-      <c r="E4">
         <v>0.027817</v>
-      </c>
-      <c r="F4">
-        <v>0.021914</v>
-      </c>
-      <c r="G4">
-        <v>0.026842</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>0.025776</v>
+        <v>0.022293</v>
       </c>
       <c r="C5">
-        <v>0.036006</v>
-      </c>
-      <c r="D5">
-        <v>0.022293</v>
-      </c>
-      <c r="E5">
         <v>0.032338</v>
-      </c>
-      <c r="F5">
-        <v>0.025951</v>
-      </c>
-      <c r="G5">
-        <v>0.031246</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>0.018742</v>
+        <v>0.024334</v>
       </c>
       <c r="C6">
-        <v>0.026623</v>
-      </c>
-      <c r="D6">
-        <v>0.024334</v>
-      </c>
-      <c r="E6">
         <v>0.039027</v>
-      </c>
-      <c r="F6">
-        <v>0.024834</v>
-      </c>
-      <c r="G6">
-        <v>0.032751</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>0.051958</v>
+        <v>0.041315</v>
       </c>
       <c r="C7">
-        <v>0.06867</v>
-      </c>
-      <c r="D7">
-        <v>0.041315</v>
-      </c>
-      <c r="E7">
         <v>0.049645</v>
-      </c>
-      <c r="F7">
-        <v>0.060635</v>
-      </c>
-      <c r="G7">
-        <v>0.071506</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>0.028188</v>
+        <v>0.025817</v>
       </c>
       <c r="C8">
-        <v>0.042752</v>
-      </c>
-      <c r="D8">
-        <v>0.025817</v>
-      </c>
-      <c r="E8">
         <v>0.03831</v>
-      </c>
-      <c r="F8">
-        <v>0.032068</v>
-      </c>
-      <c r="G8">
-        <v>0.039044</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0.025791</v>
+        <v>0.023634</v>
       </c>
       <c r="C9">
-        <v>0.033531</v>
-      </c>
-      <c r="D9">
-        <v>0.023634</v>
-      </c>
-      <c r="E9">
         <v>0.030759</v>
-      </c>
-      <c r="F9">
-        <v>0.028231</v>
-      </c>
-      <c r="G9">
-        <v>0.035615</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>0.226227</v>
+        <v>0.089919</v>
       </c>
       <c r="C10">
-        <v>0.279952</v>
-      </c>
-      <c r="D10">
-        <v>0.089919</v>
-      </c>
-      <c r="E10">
         <v>0.109586</v>
-      </c>
-      <c r="F10">
-        <v>0.078603</v>
-      </c>
-      <c r="G10">
-        <v>0.084945</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11">
-        <v>0.035318</v>
+        <v>0.028457</v>
       </c>
       <c r="C11">
-        <v>0.050742</v>
-      </c>
-      <c r="D11">
-        <v>0.028457</v>
-      </c>
-      <c r="E11">
         <v>0.043337</v>
-      </c>
-      <c r="F11">
-        <v>0.038754</v>
-      </c>
-      <c r="G11">
-        <v>0.051048</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>0.029393</v>
+        <v>0.027214</v>
       </c>
       <c r="C12">
-        <v>0.039815</v>
-      </c>
-      <c r="D12">
-        <v>0.027214</v>
-      </c>
-      <c r="E12">
         <v>0.034697</v>
-      </c>
-      <c r="F12">
-        <v>0.054449</v>
-      </c>
-      <c r="G12">
-        <v>0.061094</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>0.043329</v>
+        <v>0.03594</v>
       </c>
       <c r="C13">
-        <v>0.055249</v>
-      </c>
-      <c r="D13">
-        <v>0.03594</v>
-      </c>
-      <c r="E13">
         <v>0.046891</v>
-      </c>
-      <c r="F13">
-        <v>0.065932</v>
-      </c>
-      <c r="G13">
-        <v>0.074619</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>0.027607</v>
+        <v>0.020567</v>
       </c>
       <c r="C14">
-        <v>0.040255</v>
-      </c>
-      <c r="D14">
-        <v>0.020567</v>
-      </c>
-      <c r="E14">
         <v>0.028342</v>
-      </c>
-      <c r="F14">
-        <v>0.025242</v>
-      </c>
-      <c r="G14">
-        <v>0.032627</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>0.040027</v>
+        <v>0.029379</v>
       </c>
       <c r="C15">
-        <v>0.053746</v>
-      </c>
-      <c r="D15">
-        <v>0.029379</v>
-      </c>
-      <c r="E15">
         <v>0.040167</v>
-      </c>
-      <c r="F15">
-        <v>0.03344</v>
-      </c>
-      <c r="G15">
-        <v>0.044617</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>0.036385</v>
+      </c>
+      <c r="C16">
+        <v>0.046748</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17">
+        <v>0.013137</v>
+      </c>
+      <c r="C17">
+        <v>0.020277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B16">
-        <v>0.050531</v>
-      </c>
-      <c r="C16">
-        <v>0.064365</v>
-      </c>
-      <c r="D16">
-        <v>0.036385</v>
-      </c>
-      <c r="E16">
-        <v>0.046748</v>
-      </c>
-      <c r="F16">
-        <v>0.04083</v>
-      </c>
-      <c r="G16">
-        <v>0.050964</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.050577</v>
+      </c>
+      <c r="C18">
+        <v>0.063715</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B17">
-        <v>0.018327</v>
-      </c>
-      <c r="C17">
-        <v>0.026651</v>
-      </c>
-      <c r="D17">
-        <v>0.013137</v>
-      </c>
-      <c r="E17">
-        <v>0.020277</v>
-      </c>
-      <c r="F17">
-        <v>0.021718</v>
-      </c>
-      <c r="G17">
-        <v>0.029369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.06412</v>
+      </c>
+      <c r="C19">
+        <v>0.076185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>41</v>
       </c>
-      <c r="B18">
-        <v>0.087945</v>
-      </c>
-      <c r="C18">
-        <v>0.110721</v>
-      </c>
-      <c r="D18">
-        <v>0.050577</v>
-      </c>
-      <c r="E18">
-        <v>0.063715</v>
-      </c>
-      <c r="F18">
-        <v>0.082871</v>
-      </c>
-      <c r="G18">
-        <v>0.09389</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.034367</v>
+      </c>
+      <c r="C20">
+        <v>0.056614</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B19">
-        <v>0.368597</v>
-      </c>
-      <c r="C19">
-        <v>0.455815</v>
-      </c>
-      <c r="D19">
-        <v>0.06412</v>
-      </c>
-      <c r="E19">
-        <v>0.076185</v>
-      </c>
-      <c r="F19">
-        <v>0.101996</v>
-      </c>
-      <c r="G19">
-        <v>0.119757</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>0.027029</v>
+      </c>
+      <c r="C21">
+        <v>0.03383</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B20">
-        <v>0.041368</v>
-      </c>
-      <c r="C20">
-        <v>0.06151</v>
-      </c>
-      <c r="D20">
-        <v>0.034367</v>
-      </c>
-      <c r="E20">
-        <v>0.056614</v>
-      </c>
-      <c r="F20">
-        <v>0.044412</v>
-      </c>
-      <c r="G20">
-        <v>0.062068</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>0.028373</v>
+      </c>
+      <c r="C22">
+        <v>0.045273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="B21">
-        <v>0.041755</v>
-      </c>
-      <c r="C21">
-        <v>0.051806</v>
-      </c>
-      <c r="D21">
-        <v>0.027029</v>
-      </c>
-      <c r="E21">
-        <v>0.03383</v>
-      </c>
-      <c r="F21">
-        <v>0.043289</v>
-      </c>
-      <c r="G21">
-        <v>0.049409</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22">
-        <v>0.025248</v>
-      </c>
-      <c r="C22">
-        <v>0.034496</v>
-      </c>
-      <c r="D22">
-        <v>0.028373</v>
-      </c>
-      <c r="E22">
-        <v>0.045273</v>
-      </c>
-      <c r="F22">
-        <v>0.029584</v>
-      </c>
-      <c r="G22">
-        <v>0.035433</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
       <c r="B23">
-        <v>0.063165</v>
+        <v>0.037721</v>
       </c>
       <c r="C23">
-        <v>0.085006</v>
-      </c>
-      <c r="D23">
-        <v>0.037721</v>
-      </c>
-      <c r="E23">
         <v>0.049748</v>
       </c>
-      <c r="F23">
-        <v>0.042033</v>
-      </c>
-      <c r="G23">
-        <v>0.047258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <f t="shared" ref="B24:G24" si="0">AVERAGE(B3:B23)</f>
-        <v>0.0616037142857143</v>
+        <f xml:space="preserve">AVERAGE(B3:B23)</f>
+        <v>0.0333959523809524</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
-        <v>0.0799305238095238</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>0.0333959523809524</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C23)</f>
         <v>0.0449627619047619</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>0.0441640952380952</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>0.0528648571428571</v>
       </c>
     </row>
   </sheetData>
@@ -2337,115 +1812,63 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3">
-        <v>0.027631</v>
+        <v>0.042226</v>
       </c>
       <c r="C3">
-        <v>0.034645</v>
-      </c>
-      <c r="D3">
-        <v>0.042226</v>
-      </c>
-      <c r="E3">
         <v>0.049477</v>
-      </c>
-      <c r="F3">
-        <v>0.063115</v>
-      </c>
-      <c r="G3">
-        <v>0.071205</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4">
-        <v>0.023835</v>
+        <v>0.026209</v>
       </c>
       <c r="C4">
-        <v>0.029343</v>
-      </c>
-      <c r="D4">
-        <v>0.026209</v>
-      </c>
-      <c r="E4">
         <v>0.033681</v>
-      </c>
-      <c r="F4">
-        <v>0.025678</v>
-      </c>
-      <c r="G4">
-        <v>0.032524</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <f t="shared" ref="B5:G5" si="0">AVERAGE(B3:B4)</f>
-        <v>0.025733</v>
+        <f xml:space="preserve">AVERAGE(B3:B4)</f>
+        <v>0.0342175</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
-        <v>0.031994</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.0342175</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C4)</f>
         <v>0.041579</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>0.0443965</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>0.0518645</v>
       </c>
     </row>
   </sheetData>
@@ -2476,253 +1899,129 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>0.044542</v>
+        <v>0.035628</v>
       </c>
       <c r="C3">
-        <v>0.059457</v>
-      </c>
-      <c r="D3">
-        <v>0.035628</v>
-      </c>
-      <c r="E3">
         <v>0.047139</v>
-      </c>
-      <c r="F3">
-        <v>0.037845</v>
-      </c>
-      <c r="G3">
-        <v>0.048607</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4">
-        <v>0.052626</v>
+        <v>0.032301</v>
       </c>
       <c r="C4">
-        <v>0.065856</v>
-      </c>
-      <c r="D4">
-        <v>0.032301</v>
-      </c>
-      <c r="E4">
         <v>0.04053</v>
-      </c>
-      <c r="F4">
-        <v>0.045505</v>
-      </c>
-      <c r="G4">
-        <v>0.058218</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5">
-        <v>0.041069</v>
+        <v>0.033634</v>
       </c>
       <c r="C5">
-        <v>0.054672</v>
-      </c>
-      <c r="D5">
-        <v>0.033634</v>
-      </c>
-      <c r="E5">
         <v>0.039373</v>
-      </c>
-      <c r="F5">
-        <v>0.083671</v>
-      </c>
-      <c r="G5">
-        <v>0.090164</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B6">
-        <v>0.04537</v>
+        <v>0.035648</v>
       </c>
       <c r="C6">
-        <v>0.060382</v>
-      </c>
-      <c r="D6">
-        <v>0.035648</v>
-      </c>
-      <c r="E6">
         <v>0.045168</v>
-      </c>
-      <c r="F6">
-        <v>0.036796</v>
-      </c>
-      <c r="G6">
-        <v>0.048423</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7">
-        <v>0.057801</v>
+        <v>0.039957</v>
       </c>
       <c r="C7">
-        <v>0.075216</v>
-      </c>
-      <c r="D7">
-        <v>0.039957</v>
-      </c>
-      <c r="E7">
         <v>0.053087</v>
-      </c>
-      <c r="F7">
-        <v>0.046717</v>
-      </c>
-      <c r="G7">
-        <v>0.060976</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B8">
-        <v>0.04318</v>
+        <v>0.033369</v>
       </c>
       <c r="C8">
-        <v>0.057788</v>
-      </c>
-      <c r="D8">
-        <v>0.033369</v>
-      </c>
-      <c r="E8">
         <v>0.045369</v>
-      </c>
-      <c r="F8">
-        <v>0.036472</v>
-      </c>
-      <c r="G8">
-        <v>0.047767</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9">
-        <v>0.053301</v>
+        <v>0.040016</v>
       </c>
       <c r="C9">
-        <v>0.066625</v>
-      </c>
-      <c r="D9">
-        <v>0.040016</v>
-      </c>
-      <c r="E9">
         <v>0.053645</v>
-      </c>
-      <c r="F9">
-        <v>0.046634</v>
-      </c>
-      <c r="G9">
-        <v>0.059967</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>0.053111</v>
+        <v>0.039322</v>
       </c>
       <c r="C10">
-        <v>0.067747</v>
-      </c>
-      <c r="D10">
-        <v>0.039322</v>
-      </c>
-      <c r="E10">
         <v>0.049735</v>
-      </c>
-      <c r="F10">
-        <v>0.060859</v>
-      </c>
-      <c r="G10">
-        <v>0.072098</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <f t="shared" ref="B11:G11" si="0">AVERAGE(B3:B10)</f>
-        <v>0.048875</v>
+        <f xml:space="preserve">AVERAGE(B3:B10)</f>
+        <v>0.036234375</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
-        <v>0.063467875</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>0.036234375</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C10)</f>
         <v>0.04675575</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>0.049312375</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>0.0607775</v>
       </c>
     </row>
   </sheetData>
@@ -2749,506 +2048,250 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3">
-        <v>0.040808</v>
+        <v>0.042156</v>
       </c>
       <c r="C3">
-        <v>0.053783</v>
-      </c>
-      <c r="D3">
-        <v>0.042156</v>
-      </c>
-      <c r="E3">
         <v>0.05733</v>
-      </c>
-      <c r="F3">
-        <v>0.042571</v>
-      </c>
-      <c r="G3">
-        <v>0.061383</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4">
-        <v>0.028073</v>
+        <v>0.020538</v>
       </c>
       <c r="C4">
-        <v>0.039289</v>
-      </c>
-      <c r="D4">
-        <v>0.020538</v>
-      </c>
-      <c r="E4">
         <v>0.031033</v>
-      </c>
-      <c r="F4">
-        <v>0.019544</v>
-      </c>
-      <c r="G4">
-        <v>0.027048</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5">
-        <v>0.042842</v>
+        <v>0.026129</v>
       </c>
       <c r="C5">
-        <v>0.059794</v>
-      </c>
-      <c r="D5">
-        <v>0.026129</v>
-      </c>
-      <c r="E5">
         <v>0.035433</v>
-      </c>
-      <c r="F5">
-        <v>0.041292</v>
-      </c>
-      <c r="G5">
-        <v>0.053557</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>0.051323</v>
+        <v>0.038768</v>
       </c>
       <c r="C6">
-        <v>0.073131</v>
-      </c>
-      <c r="D6">
-        <v>0.038768</v>
-      </c>
-      <c r="E6">
         <v>0.059571</v>
-      </c>
-      <c r="F6">
-        <v>0.045748</v>
-      </c>
-      <c r="G6">
-        <v>0.060918</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7">
-        <v>0.037025</v>
+        <v>0.024962</v>
       </c>
       <c r="C7">
-        <v>0.049127</v>
-      </c>
-      <c r="D7">
-        <v>0.024962</v>
-      </c>
-      <c r="E7">
         <v>0.035498</v>
-      </c>
-      <c r="F7">
-        <v>0.02415</v>
-      </c>
-      <c r="G7">
-        <v>0.032512</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8">
-        <v>0.053735</v>
+        <v>0.046712</v>
       </c>
       <c r="C8">
-        <v>0.077568</v>
-      </c>
-      <c r="D8">
-        <v>0.046712</v>
-      </c>
-      <c r="E8">
         <v>0.068398</v>
-      </c>
-      <c r="F8">
-        <v>0.055099</v>
-      </c>
-      <c r="G8">
-        <v>0.072401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9">
-        <v>0.043207</v>
+        <v>0.028476</v>
       </c>
       <c r="C9">
-        <v>0.06185</v>
-      </c>
-      <c r="D9">
-        <v>0.028476</v>
-      </c>
-      <c r="E9">
         <v>0.037953</v>
-      </c>
-      <c r="F9">
-        <v>0.035142</v>
-      </c>
-      <c r="G9">
-        <v>0.043383</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B10">
-        <v>0.024188</v>
+        <v>0.015354</v>
       </c>
       <c r="C10">
-        <v>0.031338</v>
-      </c>
-      <c r="D10">
-        <v>0.015354</v>
-      </c>
-      <c r="E10">
         <v>0.01993</v>
-      </c>
-      <c r="F10">
-        <v>0.020183</v>
-      </c>
-      <c r="G10">
-        <v>0.025551</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11">
-        <v>0.054459</v>
+        <v>0.045647</v>
       </c>
       <c r="C11">
-        <v>0.077109</v>
-      </c>
-      <c r="D11">
-        <v>0.045647</v>
-      </c>
-      <c r="E11">
         <v>0.066318</v>
-      </c>
-      <c r="F11">
-        <v>0.047234</v>
-      </c>
-      <c r="G11">
-        <v>0.066439</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12">
-        <v>0.044353</v>
+        <v>0.043125</v>
       </c>
       <c r="C12">
-        <v>0.06288</v>
-      </c>
-      <c r="D12">
-        <v>0.043125</v>
-      </c>
-      <c r="E12">
         <v>0.059235</v>
-      </c>
-      <c r="F12">
-        <v>0.049337</v>
-      </c>
-      <c r="G12">
-        <v>0.066018</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B13">
-        <v>0.034714</v>
+        <v>0.028371</v>
       </c>
       <c r="C13">
-        <v>0.043133</v>
-      </c>
-      <c r="D13">
-        <v>0.028371</v>
-      </c>
-      <c r="E13">
         <v>0.037049</v>
-      </c>
-      <c r="F13">
-        <v>0.028203</v>
-      </c>
-      <c r="G13">
-        <v>0.037041</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B14">
-        <v>0.054722</v>
+        <v>0.044121</v>
       </c>
       <c r="C14">
-        <v>0.068753</v>
-      </c>
-      <c r="D14">
-        <v>0.044121</v>
-      </c>
-      <c r="E14">
         <v>0.056924</v>
-      </c>
-      <c r="F14">
-        <v>0.049222</v>
-      </c>
-      <c r="G14">
-        <v>0.061819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15">
-        <v>0.040608</v>
+        <v>0.028591</v>
       </c>
       <c r="C15">
-        <v>0.057795</v>
-      </c>
-      <c r="D15">
-        <v>0.028591</v>
-      </c>
-      <c r="E15">
         <v>0.041303</v>
-      </c>
-      <c r="F15">
-        <v>0.044988</v>
-      </c>
-      <c r="G15">
-        <v>0.058089</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <v>0.041215</v>
+      </c>
+      <c r="C16">
+        <v>0.053434</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17">
+        <v>0.05665</v>
+      </c>
+      <c r="C17">
+        <v>0.078006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>70</v>
       </c>
-      <c r="B16">
-        <v>0.051576</v>
-      </c>
-      <c r="C16">
-        <v>0.073173</v>
-      </c>
-      <c r="D16">
-        <v>0.041215</v>
-      </c>
-      <c r="E16">
-        <v>0.053434</v>
-      </c>
-      <c r="F16">
-        <v>0.043466</v>
-      </c>
-      <c r="G16">
-        <v>0.057757</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.02157</v>
+      </c>
+      <c r="C18">
+        <v>0.028893</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>71</v>
       </c>
-      <c r="B17">
-        <v>0.057269</v>
-      </c>
-      <c r="C17">
-        <v>0.078193</v>
-      </c>
-      <c r="D17">
-        <v>0.05665</v>
-      </c>
-      <c r="E17">
-        <v>0.078006</v>
-      </c>
-      <c r="F17">
-        <v>0.053564</v>
-      </c>
-      <c r="G17">
-        <v>0.070649</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.037153</v>
+      </c>
+      <c r="C19">
+        <v>0.05213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>72</v>
       </c>
-      <c r="B18">
-        <v>0.047983</v>
-      </c>
-      <c r="C18">
-        <v>0.062118</v>
-      </c>
-      <c r="D18">
-        <v>0.02157</v>
-      </c>
-      <c r="E18">
-        <v>0.028893</v>
-      </c>
-      <c r="F18">
-        <v>0.048195</v>
-      </c>
-      <c r="G18">
-        <v>0.065512</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.035643</v>
+      </c>
+      <c r="C20">
+        <v>0.04929</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>73</v>
       </c>
-      <c r="B19">
-        <v>0.048405</v>
-      </c>
-      <c r="C19">
-        <v>0.067409</v>
-      </c>
-      <c r="D19">
-        <v>0.037153</v>
-      </c>
-      <c r="E19">
-        <v>0.05213</v>
-      </c>
-      <c r="F19">
-        <v>0.043345</v>
-      </c>
-      <c r="G19">
-        <v>0.060061</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20">
-        <v>0.044262</v>
-      </c>
-      <c r="C20">
-        <v>0.060222</v>
-      </c>
-      <c r="D20">
-        <v>0.035643</v>
-      </c>
-      <c r="E20">
-        <v>0.04929</v>
-      </c>
-      <c r="F20">
-        <v>0.043306</v>
-      </c>
-      <c r="G20">
-        <v>0.056596</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
       <c r="B21">
-        <v>0.047076</v>
+        <v>0.028233</v>
       </c>
       <c r="C21">
-        <v>0.065504</v>
-      </c>
-      <c r="D21">
-        <v>0.028233</v>
-      </c>
-      <c r="E21">
         <v>0.037404</v>
       </c>
-      <c r="F21">
-        <v>0.043315</v>
-      </c>
-      <c r="G21">
-        <v>0.058671</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:G22" si="0">AVERAGE(B3:B21)</f>
-        <v>0.0445593684210526</v>
+        <f xml:space="preserve">AVERAGE(B3:B21)</f>
+        <v>0.0343902105263158</v>
       </c>
       <c r="C22">
-        <f t="shared" si="0"/>
-        <v>0.0611667894736842</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>0.0343902105263158</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C21)</f>
         <v>0.0476385263157895</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>0.0409423157894737</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>0.054495</v>
       </c>
     </row>
   </sheetData>
@@ -3280,388 +2323,192 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3">
-        <v>0.095737</v>
+        <v>0.063896</v>
       </c>
       <c r="C3">
-        <v>0.123396</v>
-      </c>
-      <c r="D3">
-        <v>0.063896</v>
-      </c>
-      <c r="E3">
         <v>0.082274</v>
-      </c>
-      <c r="F3">
-        <v>0.117125</v>
-      </c>
-      <c r="G3">
-        <v>0.130095</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4">
-        <v>0.034417</v>
+        <v>0.017415</v>
       </c>
       <c r="C4">
-        <v>0.045804</v>
-      </c>
-      <c r="D4">
-        <v>0.017415</v>
-      </c>
-      <c r="E4">
         <v>0.022979</v>
-      </c>
-      <c r="F4">
-        <v>0.033682</v>
-      </c>
-      <c r="G4">
-        <v>0.042553</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B5">
-        <v>0.062468</v>
+        <v>0.021192</v>
       </c>
       <c r="C5">
-        <v>0.089747</v>
-      </c>
-      <c r="D5">
-        <v>0.021192</v>
-      </c>
-      <c r="E5">
         <v>0.027142</v>
-      </c>
-      <c r="F5">
-        <v>0.027576</v>
-      </c>
-      <c r="G5">
-        <v>0.033987</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6">
-        <v>0.048639</v>
+        <v>0.029307</v>
       </c>
       <c r="C6">
-        <v>0.05689</v>
-      </c>
-      <c r="D6">
-        <v>0.029307</v>
-      </c>
-      <c r="E6">
         <v>0.036756</v>
-      </c>
-      <c r="F6">
-        <v>0.045881</v>
-      </c>
-      <c r="G6">
-        <v>0.052942</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7">
-        <v>0.039883</v>
+        <v>0.03071</v>
       </c>
       <c r="C7">
-        <v>0.053642</v>
-      </c>
-      <c r="D7">
-        <v>0.03071</v>
-      </c>
-      <c r="E7">
         <v>0.038702</v>
-      </c>
-      <c r="F7">
-        <v>0.040675</v>
-      </c>
-      <c r="G7">
-        <v>0.049606</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8">
-        <v>0.031794</v>
+        <v>0.02455</v>
       </c>
       <c r="C8">
-        <v>0.045599</v>
-      </c>
-      <c r="D8">
-        <v>0.02455</v>
-      </c>
-      <c r="E8">
         <v>0.033029</v>
-      </c>
-      <c r="F8">
-        <v>0.043142</v>
-      </c>
-      <c r="G8">
-        <v>0.050625</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9">
-        <v>0.053359</v>
+        <v>0.026735</v>
       </c>
       <c r="C9">
-        <v>0.067115</v>
-      </c>
-      <c r="D9">
-        <v>0.026735</v>
-      </c>
-      <c r="E9">
         <v>0.034985</v>
-      </c>
-      <c r="F9">
-        <v>0.052919</v>
-      </c>
-      <c r="G9">
-        <v>0.063334</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10">
-        <v>0.036949</v>
+        <v>0.030516</v>
       </c>
       <c r="C10">
-        <v>0.046526</v>
-      </c>
-      <c r="D10">
-        <v>0.030516</v>
-      </c>
-      <c r="E10">
         <v>0.03768</v>
-      </c>
-      <c r="F10">
-        <v>0.052999</v>
-      </c>
-      <c r="G10">
-        <v>0.06417</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B11">
-        <v>0.033924</v>
+        <v>0.023679</v>
       </c>
       <c r="C11">
-        <v>0.0429</v>
-      </c>
-      <c r="D11">
-        <v>0.023679</v>
-      </c>
-      <c r="E11">
         <v>0.031466</v>
-      </c>
-      <c r="F11">
-        <v>0.029415</v>
-      </c>
-      <c r="G11">
-        <v>0.037274</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12">
-        <v>0.035046</v>
+        <v>0.038349</v>
       </c>
       <c r="C12">
-        <v>0.043553</v>
-      </c>
-      <c r="D12">
-        <v>0.038349</v>
-      </c>
-      <c r="E12">
         <v>0.047985</v>
-      </c>
-      <c r="F12">
-        <v>0.031261</v>
-      </c>
-      <c r="G12">
-        <v>0.038345</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13">
-        <v>0.048273</v>
+        <v>0.031016</v>
       </c>
       <c r="C13">
-        <v>0.06292</v>
-      </c>
-      <c r="D13">
-        <v>0.031016</v>
-      </c>
-      <c r="E13">
         <v>0.039666</v>
-      </c>
-      <c r="F13">
-        <v>0.047455</v>
-      </c>
-      <c r="G13">
-        <v>0.059505</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14">
-        <v>0.027266</v>
+        <v>0.018026</v>
       </c>
       <c r="C14">
-        <v>0.035069</v>
-      </c>
-      <c r="D14">
-        <v>0.018026</v>
-      </c>
-      <c r="E14">
         <v>0.023116</v>
-      </c>
-      <c r="F14">
-        <v>0.043297</v>
-      </c>
-      <c r="G14">
-        <v>0.051595</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15">
-        <v>0.056949</v>
+        <v>0.036458</v>
       </c>
       <c r="C15">
-        <v>0.073864</v>
-      </c>
-      <c r="D15">
-        <v>0.036458</v>
-      </c>
-      <c r="E15">
         <v>0.050938</v>
-      </c>
-      <c r="F15">
-        <v>0.135624</v>
-      </c>
-      <c r="G15">
-        <v>0.154251</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16">
-        <v>0.031566</v>
+        <v>0.030046</v>
       </c>
       <c r="C16">
-        <v>0.038259</v>
-      </c>
-      <c r="D16">
-        <v>0.030046</v>
-      </c>
-      <c r="E16">
         <v>0.039062</v>
       </c>
-      <c r="F16">
-        <v>0.035355</v>
-      </c>
-      <c r="G16">
-        <v>0.042579</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <f t="shared" ref="B17:G17" si="0">AVERAGE(B3:B16)</f>
-        <v>0.0454478571428571</v>
+        <f xml:space="preserve">AVERAGE(B3:B16)</f>
+        <v>0.0301353571428571</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
-        <v>0.0589488571428572</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>0.0301353571428571</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C16)</f>
         <v>0.0389842857142857</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>0.0526004285714286</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>0.0622043571428572</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="2"/>
     </row>
   </sheetData>
